--- a/exports/trend_1d/JUBLFOOD_full_report.xlsx
+++ b/exports/trend_1d/JUBLFOOD_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q73"/>
+  <dimension ref="A1:U73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>9.51</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42088</v>
+        <v>42089</v>
       </c>
       <c r="H2" t="n">
-        <v>152.45</v>
+        <v>149.1</v>
       </c>
       <c r="I2" t="n">
         <v>150.9684156019056</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K2" t="n">
-        <v>7.81</v>
+        <v>5.45</v>
       </c>
       <c r="L2" t="n">
         <v>6.12</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>12.63</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42137</v>
+        <v>42138</v>
       </c>
       <c r="H3" t="n">
-        <v>155.15</v>
+        <v>156.65</v>
       </c>
       <c r="I3" t="n">
         <v>156.61948684926</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K3" t="n">
-        <v>-4.06</v>
+        <v>-5.06</v>
       </c>
       <c r="L3" t="n">
         <v>9.76</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>11.76</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42208</v>
+        <v>42209</v>
       </c>
       <c r="H4" t="n">
-        <v>184.25</v>
+        <v>181.05</v>
       </c>
       <c r="I4" t="n">
         <v>181.2936347963039</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K4" t="n">
-        <v>17.62</v>
+        <v>15.58</v>
       </c>
       <c r="L4" t="n">
         <v>1.69</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>8</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42222</v>
+        <v>42223</v>
       </c>
       <c r="H5" t="n">
-        <v>189.25</v>
+        <v>193.1</v>
       </c>
       <c r="I5" t="n">
         <v>191.5187459354187</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K5" t="n">
-        <v>-4.53</v>
+        <v>-6.66</v>
       </c>
       <c r="L5" t="n">
-        <v>6.32</v>
+        <v>7.59</v>
       </c>
       <c r="M5" t="n">
         <v>0.85</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>8.539999999999999</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42228</v>
+        <v>42229</v>
       </c>
       <c r="H6" t="n">
-        <v>181.7</v>
+        <v>176.45</v>
       </c>
       <c r="I6" t="n">
         <v>177.5178361679175</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K6" t="n">
-        <v>-5.9</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>6.5</v>
+        <v>10.54</v>
       </c>
       <c r="M6" t="n">
         <v>0.52</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>11.47</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42331</v>
+        <v>42332</v>
       </c>
       <c r="H7" t="n">
-        <v>145.9</v>
+        <v>152.5</v>
       </c>
       <c r="I7" t="n">
         <v>151.9893150800788</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K7" t="n">
-        <v>17.31</v>
+        <v>13.57</v>
       </c>
       <c r="L7" t="n">
         <v>4.62</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>13.16</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42376</v>
+        <v>42377</v>
       </c>
       <c r="H8" t="n">
-        <v>139.55</v>
+        <v>136.25</v>
       </c>
       <c r="I8" t="n">
         <v>138.635409606053</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K8" t="n">
-        <v>-8.49</v>
+        <v>-10.66</v>
       </c>
       <c r="L8" t="n">
-        <v>8.85</v>
+        <v>11.11</v>
       </c>
       <c r="M8" t="n">
         <v>1.16</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>11.48</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42433</v>
+        <v>42437</v>
       </c>
       <c r="H9" t="n">
-        <v>113.35</v>
+        <v>118.05</v>
       </c>
       <c r="I9" t="n">
         <v>116.2836424263661</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K9" t="n">
-        <v>16.81</v>
+        <v>13.36</v>
       </c>
       <c r="L9" t="n">
         <v>4.37</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>18.55</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42488</v>
+        <v>42489</v>
       </c>
       <c r="H10" t="n">
-        <v>119.05</v>
+        <v>115.7</v>
       </c>
       <c r="I10" t="n">
         <v>118.404350742405</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K10" t="n">
-        <v>0.85</v>
+        <v>-1.99</v>
       </c>
       <c r="L10" t="n">
         <v>7.33</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>17.92</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42551</v>
+        <v>42552</v>
       </c>
       <c r="H11" t="n">
-        <v>113.6</v>
+        <v>117.4</v>
       </c>
       <c r="I11" t="n">
         <v>115.0025977951577</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K11" t="n">
-        <v>1.82</v>
+        <v>-1.47</v>
       </c>
       <c r="L11" t="n">
         <v>5.45</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>11.97</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42615</v>
+        <v>42619</v>
       </c>
       <c r="H12" t="n">
-        <v>118.3</v>
+        <v>106.8</v>
       </c>
       <c r="I12" t="n">
         <v>114.9732374402247</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K12" t="n">
-        <v>0.77</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>4.34</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>0.76</v>
+        <v>6.17</v>
       </c>
       <c r="N12" t="n">
-        <v>5.64</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="O12" t="n">
         <v>3.35</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42579</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>15.51</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42661</v>
+        <v>42662</v>
       </c>
       <c r="H13" t="n">
-        <v>105</v>
+        <v>108.5</v>
       </c>
       <c r="I13" t="n">
         <v>106.3646285090296</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K13" t="n">
-        <v>1.69</v>
+        <v>-1.59</v>
       </c>
       <c r="L13" t="n">
         <v>5.2</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,25 +1385,25 @@
         <v>10.4</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42669</v>
+        <v>42670</v>
       </c>
       <c r="H14" t="n">
-        <v>105.75</v>
+        <v>99.55</v>
       </c>
       <c r="I14" t="n">
         <v>101.0779917239642</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.53</v>
+        <v>-8.25</v>
       </c>
       <c r="L14" t="n">
-        <v>3.78</v>
+        <v>8.76</v>
       </c>
       <c r="M14" t="n">
-        <v>0.76</v>
+        <v>1.61</v>
       </c>
       <c r="N14" t="n">
         <v>7.8</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>17.76</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42737</v>
+        <v>42738</v>
       </c>
       <c r="H15" t="n">
-        <v>86</v>
+        <v>86.75</v>
       </c>
       <c r="I15" t="n">
         <v>86.2807025256308</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K15" t="n">
-        <v>13.61</v>
+        <v>12.86</v>
       </c>
       <c r="L15" t="n">
         <v>4.67</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>9.73</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42832</v>
+        <v>42835</v>
       </c>
       <c r="H16" t="n">
-        <v>104</v>
+        <v>102.9</v>
       </c>
       <c r="I16" t="n">
         <v>103.8295337850716</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="K16" t="n">
-        <v>19.88</v>
+        <v>18.62</v>
       </c>
       <c r="L16" t="n">
         <v>5.59</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>4</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1389,25 +1592,25 @@
         <v>9.109999999999999</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42919</v>
+        <v>42920</v>
       </c>
       <c r="H17" t="n">
-        <v>99.90000000000001</v>
+        <v>102.55</v>
       </c>
       <c r="I17" t="n">
         <v>99.9830280932031</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K17" t="n">
-        <v>2.92</v>
+        <v>0.34</v>
       </c>
       <c r="L17" t="n">
         <v>6.95</v>
       </c>
       <c r="M17" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="N17" t="n">
         <v>5.55</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42852</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>8.5</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43075</v>
+        <v>43076</v>
       </c>
       <c r="H18" t="n">
-        <v>170.55</v>
+        <v>165.05</v>
       </c>
       <c r="I18" t="n">
         <v>166.7378278670132</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K18" t="n">
-        <v>66.31</v>
+        <v>60.95</v>
       </c>
       <c r="L18" t="n">
         <v>1.32</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>107</v>
+        <v>108</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>6</v>
+      </c>
+      <c r="U18" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>10.15</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43102</v>
+        <v>43103</v>
       </c>
       <c r="H19" t="n">
-        <v>179.25</v>
+        <v>185.05</v>
       </c>
       <c r="I19" t="n">
         <v>180.772860407214</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K19" t="n">
-        <v>-8.6</v>
+        <v>-12.12</v>
       </c>
       <c r="L19" t="n">
-        <v>9.359999999999999</v>
+        <v>12.51</v>
       </c>
       <c r="M19" t="n">
         <v>1.2</v>
       </c>
       <c r="N19" t="n">
-        <v>3.01</v>
+        <v>3.24</v>
       </c>
       <c r="O19" t="n">
         <v>-3.22</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,25 +1799,25 @@
         <v>8.970000000000001</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43132</v>
+        <v>43133</v>
       </c>
       <c r="H20" t="n">
-        <v>204.75</v>
+        <v>200.6</v>
       </c>
       <c r="I20" t="n">
         <v>204.0968552838042</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K20" t="n">
-        <v>10.65</v>
+        <v>8.4</v>
       </c>
       <c r="L20" t="n">
         <v>2.73</v>
       </c>
       <c r="M20" t="n">
-        <v>0.77</v>
+        <v>2.32</v>
       </c>
       <c r="N20" t="n">
         <v>4.44</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>12.48</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43179</v>
+        <v>43180</v>
       </c>
       <c r="H21" t="n">
-        <v>212.2</v>
+        <v>220.75</v>
       </c>
       <c r="I21" t="n">
         <v>217.25027455983</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K21" t="n">
-        <v>-5.78</v>
+        <v>-10.04</v>
       </c>
       <c r="L21" t="n">
-        <v>8.18</v>
+        <v>10.44</v>
       </c>
       <c r="M21" t="n">
         <v>1.43</v>
       </c>
       <c r="N21" t="n">
-        <v>3.27</v>
+        <v>4.03</v>
       </c>
       <c r="O21" t="n">
         <v>-2.03</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>10</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43234</v>
+        <v>43235</v>
       </c>
       <c r="H22" t="n">
-        <v>243.8</v>
+        <v>240.05</v>
       </c>
       <c r="I22" t="n">
         <v>242.6556146104177</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K22" t="n">
-        <v>10.44</v>
+        <v>8.74</v>
       </c>
       <c r="L22" t="n">
         <v>3.28</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>11.09</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43244</v>
+        <v>43245</v>
       </c>
       <c r="H23" t="n">
-        <v>265.35</v>
+        <v>266.2</v>
       </c>
       <c r="I23" t="n">
         <v>266.0622442367425</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K23" t="n">
-        <v>-10.54</v>
+        <v>-10.89</v>
       </c>
       <c r="L23" t="n">
-        <v>11.12</v>
+        <v>12.31</v>
       </c>
       <c r="M23" t="n">
         <v>0.9399999999999999</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>7.54</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43346</v>
+        <v>43347</v>
       </c>
       <c r="H24" t="n">
-        <v>305.25</v>
+        <v>289.75</v>
       </c>
       <c r="I24" t="n">
         <v>293.2771024496097</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K24" t="n">
-        <v>14.67</v>
+        <v>8.85</v>
       </c>
       <c r="L24" t="n">
         <v>7.21</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>5</v>
+      </c>
+      <c r="U24" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>10.53</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43434</v>
+        <v>43437</v>
       </c>
       <c r="H25" t="n">
-        <v>251.6</v>
+        <v>266</v>
       </c>
       <c r="I25" t="n">
         <v>252.0540742061816</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K25" t="n">
-        <v>13.17</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L25" t="n">
         <v>5.4</v>
@@ -1866,7 +2165,7 @@
         <v>1.4</v>
       </c>
       <c r="N25" t="n">
-        <v>4.99</v>
+        <v>5.72</v>
       </c>
       <c r="O25" t="n">
         <v>-5.08</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>4</v>
+      </c>
+      <c r="U25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>12.58</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43483</v>
+        <v>43486</v>
       </c>
       <c r="H26" t="n">
-        <v>243.6</v>
+        <v>236.1</v>
       </c>
       <c r="I26" t="n">
         <v>239.8975308771232</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K26" t="n">
-        <v>-8.42</v>
+        <v>-11.24</v>
       </c>
       <c r="L26" t="n">
         <v>13.83</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>10.5</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43496</v>
+        <v>43497</v>
       </c>
       <c r="H27" t="n">
-        <v>251.7</v>
+        <v>271.6</v>
       </c>
       <c r="I27" t="n">
         <v>255.2764549194953</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K27" t="n">
-        <v>-6.61</v>
+        <v>-15.04</v>
       </c>
       <c r="L27" t="n">
-        <v>7.58</v>
+        <v>16.16</v>
       </c>
       <c r="M27" t="n">
         <v>2.48</v>
       </c>
       <c r="N27" t="n">
-        <v>4.85</v>
+        <v>7.91</v>
       </c>
       <c r="O27" t="n">
         <v>-3.08</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>14.3</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43571</v>
+        <v>43573</v>
       </c>
       <c r="H28" t="n">
-        <v>276.25</v>
+        <v>269.05</v>
       </c>
       <c r="I28" t="n">
         <v>271.9087825871877</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K28" t="n">
-        <v>1.71</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="L28" t="n">
         <v>11.23</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>9.34</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43609</v>
+        <v>43612</v>
       </c>
       <c r="H29" t="n">
-        <v>263.4</v>
+        <v>266.8</v>
       </c>
       <c r="I29" t="n">
         <v>266.4256914652303</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K29" t="n">
-        <v>2.1</v>
+        <v>0.84</v>
       </c>
       <c r="L29" t="n">
         <v>3.44</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>11.12</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43643</v>
+        <v>43644</v>
       </c>
       <c r="H30" t="n">
-        <v>251.2</v>
+        <v>246.6</v>
       </c>
       <c r="I30" t="n">
         <v>246.6850407230392</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K30" t="n">
-        <v>-5.85</v>
+        <v>-7.57</v>
       </c>
       <c r="L30" t="n">
-        <v>6.9</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="M30" t="n">
         <v>1.59</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>9.65</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43717</v>
+        <v>43719</v>
       </c>
       <c r="H31" t="n">
-        <v>241.85</v>
+        <v>251.4</v>
       </c>
       <c r="I31" t="n">
         <v>249.3351865665198</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="K31" t="n">
-        <v>1.93</v>
+        <v>-1.95</v>
       </c>
       <c r="L31" t="n">
         <v>3.45</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>11.18</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43888</v>
+        <v>43889</v>
       </c>
       <c r="H32" t="n">
-        <v>370.6</v>
+        <v>351.35</v>
       </c>
       <c r="I32" t="n">
         <v>357.7110482686311</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K32" t="n">
-        <v>47.41</v>
+        <v>39.76</v>
       </c>
       <c r="L32" t="n">
         <v>4.08</v>
@@ -2265,7 +2648,7 @@
         <v>3.55</v>
       </c>
       <c r="N32" t="n">
-        <v>4.11</v>
+        <v>5.19</v>
       </c>
       <c r="O32" t="n">
         <v>3.95</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>117</v>
+        <v>118</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>7</v>
+      </c>
+      <c r="U32" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>11.18</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43950</v>
+        <v>43951</v>
       </c>
       <c r="H33" t="n">
-        <v>310.7</v>
+        <v>321.7</v>
       </c>
       <c r="I33" t="n">
         <v>313.0668760328103</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K33" t="n">
-        <v>11.57</v>
+        <v>8.44</v>
       </c>
       <c r="L33" t="n">
         <v>4</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>16.98</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44127</v>
+        <v>44130</v>
       </c>
       <c r="H34" t="n">
-        <v>444</v>
+        <v>432.85</v>
       </c>
       <c r="I34" t="n">
         <v>434.8011331709172</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="K34" t="n">
-        <v>38.02</v>
+        <v>34.55</v>
       </c>
       <c r="L34" t="n">
         <v>7.62</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>124</v>
+        <v>125</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>6</v>
+      </c>
+      <c r="U34" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>10.89</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44147</v>
+        <v>44148</v>
       </c>
       <c r="H35" t="n">
-        <v>467.85</v>
+        <v>496.4</v>
       </c>
       <c r="I35" t="n">
         <v>473.1987784474795</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K35" t="n">
-        <v>-8.09</v>
+        <v>-14.68</v>
       </c>
       <c r="L35" t="n">
-        <v>12.23</v>
+        <v>15.61</v>
       </c>
       <c r="M35" t="n">
-        <v>0.96</v>
+        <v>1.09</v>
       </c>
       <c r="N35" t="n">
-        <v>3.95</v>
+        <v>6.1</v>
       </c>
       <c r="O35" t="n">
         <v>-2.51</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>13.77</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44221</v>
+        <v>44223</v>
       </c>
       <c r="H36" t="n">
-        <v>543.95</v>
+        <v>527.65</v>
       </c>
       <c r="I36" t="n">
         <v>533.6362887792371</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="K36" t="n">
-        <v>9.58</v>
+        <v>6.3</v>
       </c>
       <c r="L36" t="n">
         <v>5.12</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>12.75</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44245</v>
+        <v>44246</v>
       </c>
       <c r="H37" t="n">
-        <v>580.5</v>
+        <v>590.25</v>
       </c>
       <c r="I37" t="n">
         <v>584.2450229310352</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K37" t="n">
-        <v>-10.02</v>
+        <v>-11.86</v>
       </c>
       <c r="L37" t="n">
-        <v>12.47</v>
+        <v>13.91</v>
       </c>
       <c r="M37" t="n">
         <v>3.37</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>9.94</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44272</v>
+        <v>44273</v>
       </c>
       <c r="H38" t="n">
-        <v>573.95</v>
+        <v>558.2</v>
       </c>
       <c r="I38" t="n">
         <v>564.7571323275962</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K38" t="n">
-        <v>-2.76</v>
+        <v>-5.43</v>
       </c>
       <c r="L38" t="n">
-        <v>3.37</v>
+        <v>5.87</v>
       </c>
       <c r="M38" t="n">
         <v>1.09</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>12.55</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44334</v>
+        <v>44335</v>
       </c>
       <c r="H39" t="n">
-        <v>592.8</v>
+        <v>602.9</v>
       </c>
       <c r="I39" t="n">
         <v>602.2804898802779</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K39" t="n">
-        <v>-6.2</v>
+        <v>-8.01</v>
       </c>
       <c r="L39" t="n">
-        <v>8.380000000000001</v>
+        <v>9.42</v>
       </c>
       <c r="M39" t="n">
         <v>3.84</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>10.13</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44488</v>
+        <v>44489</v>
       </c>
       <c r="H40" t="n">
-        <v>866.25</v>
+        <v>793.05</v>
       </c>
       <c r="I40" t="n">
         <v>801.4624046962222</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K40" t="n">
-        <v>43.68</v>
+        <v>31.54</v>
       </c>
       <c r="L40" t="n">
         <v>2.28</v>
@@ -2721,7 +3200,7 @@
         <v>1.94</v>
       </c>
       <c r="N40" t="n">
-        <v>4.45</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="O40" t="n">
         <v>1.7</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>106</v>
+        <v>107</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>6</v>
+      </c>
+      <c r="U40" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>18.43</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44567</v>
+        <v>44568</v>
       </c>
       <c r="H41" t="n">
-        <v>716</v>
+        <v>752.7</v>
       </c>
       <c r="I41" t="n">
         <v>747.0052050300303</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K41" t="n">
-        <v>9.720000000000001</v>
+        <v>5.09</v>
       </c>
       <c r="L41" t="n">
         <v>9.449999999999999</v>
@@ -2778,7 +3269,7 @@
         <v>3.28</v>
       </c>
       <c r="N41" t="n">
-        <v>3.06</v>
+        <v>5.13</v>
       </c>
       <c r="O41" t="n">
         <v>-8.449999999999999</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>4</v>
+      </c>
+      <c r="U41" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>11.58</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44582</v>
+        <v>44585</v>
       </c>
       <c r="H42" t="n">
-        <v>740.35</v>
+        <v>700.15</v>
       </c>
       <c r="I42" t="n">
         <v>720.8937118514165</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K42" t="n">
-        <v>-1.64</v>
+        <v>-6.98</v>
       </c>
       <c r="L42" t="n">
-        <v>4.74</v>
+        <v>7.69</v>
       </c>
       <c r="M42" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="N42" t="n">
-        <v>2.74</v>
+        <v>5.43</v>
       </c>
       <c r="O42" t="n">
         <v>5.13</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>13.54</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44671</v>
+        <v>44672</v>
       </c>
       <c r="H43" t="n">
-        <v>551.7</v>
+        <v>594.75</v>
       </c>
       <c r="I43" t="n">
         <v>582.6158650307116</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K43" t="n">
-        <v>21.2</v>
+        <v>15.05</v>
       </c>
       <c r="L43" t="n">
         <v>5.66</v>
@@ -2892,7 +3407,7 @@
         <v>4.28</v>
       </c>
       <c r="N43" t="n">
-        <v>6.67</v>
+        <v>7.8</v>
       </c>
       <c r="O43" t="n">
         <v>-5.43</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>4</v>
+      </c>
+      <c r="U43" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -2928,25 +3455,25 @@
         <v>15.23</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44686</v>
+        <v>44687</v>
       </c>
       <c r="H44" t="n">
-        <v>513.1</v>
+        <v>496.55</v>
       </c>
       <c r="I44" t="n">
         <v>508.9409822673788</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K44" t="n">
-        <v>-13.73</v>
+        <v>-16.51</v>
       </c>
       <c r="L44" t="n">
-        <v>14.33</v>
+        <v>17.24</v>
       </c>
       <c r="M44" t="n">
-        <v>1.62</v>
+        <v>3.53</v>
       </c>
       <c r="N44" t="n">
         <v>5.88</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>15.25</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44708</v>
+        <v>44711</v>
       </c>
       <c r="H45" t="n">
-        <v>516.75</v>
+        <v>566.85</v>
       </c>
       <c r="I45" t="n">
         <v>529.6835202061172</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K45" t="n">
-        <v>-4.07</v>
+        <v>-14.16</v>
       </c>
       <c r="L45" t="n">
-        <v>4.51</v>
+        <v>15.55</v>
       </c>
       <c r="M45" t="n">
-        <v>2.03</v>
+        <v>2.52</v>
       </c>
       <c r="N45" t="n">
-        <v>6.14</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="O45" t="n">
         <v>-3.23</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>17.86</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44872</v>
+        <v>44874</v>
       </c>
       <c r="H46" t="n">
-        <v>612.7</v>
+        <v>566.45</v>
       </c>
       <c r="I46" t="n">
         <v>579.660346135895</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="K46" t="n">
-        <v>8.09</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L46" t="n">
         <v>14.09</v>
@@ -3063,7 +3614,7 @@
         <v>3.55</v>
       </c>
       <c r="N46" t="n">
-        <v>5.35</v>
+        <v>7.55</v>
       </c>
       <c r="O46" t="n">
         <v>9.699999999999999</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>111</v>
+        <v>112</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>6</v>
+      </c>
+      <c r="U46" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>13.34</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45049</v>
+        <v>45050</v>
       </c>
       <c r="H47" t="n">
-        <v>458</v>
+        <v>471.9</v>
       </c>
       <c r="I47" t="n">
         <v>462.0852665178155</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K47" t="n">
-        <v>19.15</v>
+        <v>16.69</v>
       </c>
       <c r="L47" t="n">
         <v>7.69</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>119</v>
+        <v>120</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>7</v>
+      </c>
+      <c r="U47" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>8.359999999999999</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45120</v>
+        <v>45121</v>
       </c>
       <c r="H48" t="n">
-        <v>471.15</v>
+        <v>470.7</v>
       </c>
       <c r="I48" t="n">
         <v>470.8572589824737</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.16</v>
+        <v>-0.25</v>
       </c>
       <c r="L48" t="n">
         <v>4.75</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>8.06</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45141</v>
+        <v>45142</v>
       </c>
       <c r="H49" t="n">
-        <v>491.25</v>
+        <v>517.15</v>
       </c>
       <c r="I49" t="n">
         <v>498.5221693421648</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K49" t="n">
-        <v>-4.37</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>4.8</v>
+        <v>10.47</v>
       </c>
       <c r="M49" t="n">
         <v>0.5</v>
       </c>
       <c r="N49" t="n">
-        <v>2.49</v>
+        <v>5.27</v>
       </c>
       <c r="O49" t="n">
         <v>-0.1</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>9.550000000000001</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45154</v>
+        <v>45155</v>
       </c>
       <c r="H50" t="n">
-        <v>482.55</v>
+        <v>478.3</v>
       </c>
       <c r="I50" t="n">
         <v>481.588673888466</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K50" t="n">
-        <v>-6.69</v>
+        <v>-7.51</v>
       </c>
       <c r="L50" t="n">
-        <v>7.45</v>
+        <v>7.81</v>
       </c>
       <c r="M50" t="n">
         <v>0.24</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>8.69</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45173</v>
+        <v>45174</v>
       </c>
       <c r="H51" t="n">
-        <v>502.7</v>
+        <v>533.3</v>
       </c>
       <c r="I51" t="n">
         <v>515.7382965258822</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K51" t="n">
-        <v>-5.1</v>
+        <v>-11.5</v>
       </c>
       <c r="L51" t="n">
-        <v>8.5</v>
+        <v>12.88</v>
       </c>
       <c r="M51" t="n">
         <v>0.87</v>
       </c>
       <c r="N51" t="n">
-        <v>4.67</v>
+        <v>6.09</v>
       </c>
       <c r="O51" t="n">
         <v>-0.88</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>10.28</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45224</v>
+        <v>45225</v>
       </c>
       <c r="H52" t="n">
-        <v>529.1</v>
+        <v>506.05</v>
       </c>
       <c r="I52" t="n">
         <v>511.0260088583063</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.79</v>
+        <v>-5.11</v>
       </c>
       <c r="L52" t="n">
-        <v>6.04</v>
+        <v>7.13</v>
       </c>
       <c r="M52" t="n">
-        <v>1.72</v>
+        <v>3.61</v>
       </c>
       <c r="N52" t="n">
-        <v>3.23</v>
+        <v>4.36</v>
       </c>
       <c r="O52" t="n">
         <v>6.09</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>8.15</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45252</v>
+        <v>45253</v>
       </c>
       <c r="H53" t="n">
-        <v>530.4</v>
+        <v>537.55</v>
       </c>
       <c r="I53" t="n">
         <v>531.9548686790187</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K53" t="n">
-        <v>-4.81</v>
+        <v>-6.22</v>
       </c>
       <c r="L53" t="n">
-        <v>5.92</v>
+        <v>7.41</v>
       </c>
       <c r="M53" t="n">
         <v>1.04</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>6.63</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45296</v>
+        <v>45299</v>
       </c>
       <c r="H54" t="n">
-        <v>555.55</v>
+        <v>534.35</v>
       </c>
       <c r="I54" t="n">
         <v>536.0204388234117</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K54" t="n">
-        <v>3.35</v>
+        <v>-0.6</v>
       </c>
       <c r="L54" t="n">
         <v>1.88</v>
@@ -3519,7 +4166,7 @@
         <v>1.31</v>
       </c>
       <c r="N54" t="n">
-        <v>1.93</v>
+        <v>3.82</v>
       </c>
       <c r="O54" t="n">
         <v>1.35</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>9.369999999999999</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45415</v>
+        <v>45418</v>
       </c>
       <c r="H55" t="n">
-        <v>462.75</v>
+        <v>472.65</v>
       </c>
       <c r="I55" t="n">
         <v>466.7292783915864</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="K55" t="n">
-        <v>13.4</v>
+        <v>11.55</v>
       </c>
       <c r="L55" t="n">
         <v>4.15</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>5</v>
+      </c>
+      <c r="U55" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45566</v>
+        <v>45568</v>
       </c>
       <c r="H56" t="n">
-        <v>658.8</v>
+        <v>635.15</v>
       </c>
       <c r="I56" t="n">
         <v>657.6395132701214</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="K56" t="n">
-        <v>39.38</v>
+        <v>34.38</v>
       </c>
       <c r="L56" t="n">
         <v>4.28</v>
@@ -3633,7 +4304,7 @@
         <v>1.85</v>
       </c>
       <c r="N56" t="n">
-        <v>3.51</v>
+        <v>3.59</v>
       </c>
       <c r="O56" t="n">
         <v>2.14</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>104</v>
+        <v>105</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>6</v>
+      </c>
+      <c r="U56" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>9.800000000000001</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45607</v>
+        <v>45608</v>
       </c>
       <c r="H57" t="n">
-        <v>602</v>
+        <v>636.85</v>
       </c>
       <c r="I57" t="n">
         <v>617.9993202014231</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K57" t="n">
-        <v>5.22</v>
+        <v>-0.27</v>
       </c>
       <c r="L57" t="n">
-        <v>2.87</v>
+        <v>3.27</v>
       </c>
       <c r="M57" t="n">
-        <v>1.53</v>
+        <v>4.04</v>
       </c>
       <c r="N57" t="n">
-        <v>4.38</v>
+        <v>5.79</v>
       </c>
       <c r="O57" t="n">
         <v>-3.59</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>10.4</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45667</v>
+        <v>45670</v>
       </c>
       <c r="H58" t="n">
-        <v>737</v>
+        <v>706.6</v>
       </c>
       <c r="I58" t="n">
         <v>709.8600212317699</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K58" t="n">
-        <v>15.73</v>
+        <v>10.95</v>
       </c>
       <c r="L58" t="n">
         <v>5.21</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>11.1</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45688</v>
+        <v>45689</v>
       </c>
       <c r="H59" t="n">
-        <v>703.9</v>
+        <v>739.8</v>
       </c>
       <c r="I59" t="n">
         <v>732.3542204071158</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K59" t="n">
-        <v>0.38</v>
+        <v>-4.7</v>
       </c>
       <c r="L59" t="n">
-        <v>5.85</v>
+        <v>6.66</v>
       </c>
       <c r="M59" t="n">
         <v>0.86</v>
       </c>
       <c r="N59" t="n">
-        <v>4.32</v>
+        <v>5.1</v>
       </c>
       <c r="O59" t="n">
         <v>-4.12</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>14.47</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45699</v>
+        <v>45700</v>
       </c>
       <c r="H60" t="n">
-        <v>661.3</v>
+        <v>641</v>
       </c>
       <c r="I60" t="n">
         <v>646.028809152622</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K60" t="n">
-        <v>-10.61</v>
+        <v>-13.35</v>
       </c>
       <c r="L60" t="n">
-        <v>11.8</v>
+        <v>15.04</v>
       </c>
       <c r="M60" t="n">
         <v>0.65</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>15.6</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45748</v>
+        <v>45749</v>
       </c>
       <c r="H61" t="n">
-        <v>660.85</v>
+        <v>682.6</v>
       </c>
       <c r="I61" t="n">
         <v>676.9911300874244</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K61" t="n">
-        <v>-3.1</v>
+        <v>-6.49</v>
       </c>
       <c r="L61" t="n">
         <v>12.31</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>11.33</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45806</v>
+        <v>45807</v>
       </c>
       <c r="H62" t="n">
-        <v>670.35</v>
+        <v>655.55</v>
       </c>
       <c r="I62" t="n">
         <v>656.320839181463</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K62" t="n">
-        <v>-1.79</v>
+        <v>-3.96</v>
       </c>
       <c r="L62" t="n">
         <v>5.04</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>3</v>
+      </c>
+      <c r="U62" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>9.35</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45832</v>
+        <v>45833</v>
       </c>
       <c r="H63" t="n">
-        <v>695.55</v>
+        <v>713</v>
       </c>
       <c r="I63" t="n">
         <v>709.2795331953637</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K63" t="n">
-        <v>-6.1</v>
+        <v>-8.76</v>
       </c>
       <c r="L63" t="n">
-        <v>7.21</v>
+        <v>9.56</v>
       </c>
       <c r="M63" t="n">
         <v>1.3</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>8.26</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45859</v>
+        <v>45860</v>
       </c>
       <c r="H64" t="n">
-        <v>679.35</v>
+        <v>662.1</v>
       </c>
       <c r="I64" t="n">
         <v>664.0547158685639</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K64" t="n">
-        <v>-4.72</v>
+        <v>-7.14</v>
       </c>
       <c r="L64" t="n">
-        <v>5.6</v>
+        <v>7.43</v>
       </c>
       <c r="M64" t="n">
         <v>0.54</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>7.38</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="H65" t="n">
-        <v>573.5</v>
+        <v>615.3</v>
       </c>
       <c r="I65" t="n">
         <v>612.2260952242926</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K65" t="n">
-        <v>13.38</v>
+        <v>7.07</v>
       </c>
       <c r="L65" t="n">
         <v>3.1</v>
       </c>
       <c r="M65" t="n">
-        <v>2.74</v>
+        <v>5.48</v>
       </c>
       <c r="N65" t="n">
-        <v>4.63</v>
+        <v>7.29</v>
       </c>
       <c r="O65" t="n">
         <v>-2.54</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>5</v>
+      </c>
+      <c r="U65" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>8.880000000000001</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="H66" t="n">
-        <v>577.45</v>
+        <v>560.2</v>
       </c>
       <c r="I66" t="n">
         <v>566.8800398737064</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K66" t="n">
-        <v>-6.15</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="L66" t="n">
-        <v>7.27</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="M66" t="n">
         <v>0.72</v>
       </c>
       <c r="N66" t="n">
-        <v>2.4</v>
+        <v>2.99</v>
       </c>
       <c r="O66" t="n">
         <v>7.29</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>9.34</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="H67" t="n">
-        <v>516.6</v>
+        <v>545.1</v>
       </c>
       <c r="I67" t="n">
         <v>527.4769230019128</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K67" t="n">
-        <v>7.78</v>
+        <v>2.7</v>
       </c>
       <c r="L67" t="n">
         <v>3.15</v>
@@ -4260,7 +5063,7 @@
         <v>4.74</v>
       </c>
       <c r="N67" t="n">
-        <v>2.02</v>
+        <v>5.52</v>
       </c>
       <c r="O67" t="n">
         <v>-2.99</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>3</v>
+      </c>
+      <c r="U67" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -4296,25 +5111,25 @@
         <v>11.53</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="H68" t="n">
-        <v>519.9</v>
+        <v>505.65</v>
       </c>
       <c r="I68" t="n">
         <v>508.8863868448574</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K68" t="n">
-        <v>-4.62</v>
+        <v>-7.24</v>
       </c>
       <c r="L68" t="n">
-        <v>6.81</v>
+        <v>8.27</v>
       </c>
       <c r="M68" t="n">
-        <v>0.84</v>
+        <v>3.83</v>
       </c>
       <c r="N68" t="n">
         <v>3.21</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>9.6</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="H69" t="n">
-        <v>471.9</v>
+        <v>493.1</v>
       </c>
       <c r="I69" t="n">
         <v>491.7704615894447</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K69" t="n">
-        <v>6.67</v>
+        <v>2.48</v>
       </c>
       <c r="L69" t="n">
         <v>0.86</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>14.24</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="H70" t="n">
-        <v>438.75</v>
+        <v>430.05</v>
       </c>
       <c r="I70" t="n">
         <v>435.3256761393326</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K70" t="n">
-        <v>-11.02</v>
+        <v>-12.79</v>
       </c>
       <c r="L70" t="n">
         <v>14.37</v>
@@ -4440,7 +5279,19 @@
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4467,28 +5318,28 @@
         <v>12.7</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="H71" t="n">
-        <v>438.25</v>
+        <v>454.95</v>
       </c>
       <c r="I71" t="n">
         <v>450.3777247003165</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K71" t="n">
-        <v>-1.91</v>
+        <v>-5.79</v>
       </c>
       <c r="L71" t="n">
-        <v>4.63</v>
+        <v>6.36</v>
       </c>
       <c r="M71" t="n">
         <v>1.35</v>
       </c>
       <c r="N71" t="n">
-        <v>3.44</v>
+        <v>3.81</v>
       </c>
       <c r="O71" t="n">
         <v>-1.98</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>11.37</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="H72" t="n">
-        <v>470.25</v>
+        <v>466</v>
       </c>
       <c r="I72" t="n">
         <v>467.5802089596642</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="K72" t="n">
-        <v>3.36</v>
+        <v>2.43</v>
       </c>
       <c r="L72" t="n">
         <v>10.2</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>3</v>
+      </c>
+      <c r="U72" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -4605,6 +5480,14 @@
       <c r="Q73" t="n">
         <v>30</v>
       </c>
+      <c r="R73" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9563,7 +10446,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58.5</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6">
@@ -9573,7 +10456,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7">
@@ -9583,7 +10466,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="8">
@@ -9593,7 +10476,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -9603,7 +10486,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10">
@@ -9613,7 +10496,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11">
@@ -9653,7 +10536,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.92</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="15">
@@ -9663,7 +10546,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7.32</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="16">
@@ -9673,7 +10556,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.46</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="17">
@@ -9683,7 +10566,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>66.31</v>
+        <v>60.95</v>
       </c>
     </row>
     <row r="18">
@@ -9693,7 +10576,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>53.5</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="19">
@@ -9703,7 +10586,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.49</v>
+        <v>7.71</v>
       </c>
     </row>
     <row r="20">
@@ -9713,7 +10596,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.66</v>
+        <v>7.33</v>
       </c>
     </row>
     <row r="21">
@@ -9723,7 +10606,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14.37</v>
+        <v>17.24</v>
       </c>
     </row>
     <row r="22">
@@ -9733,7 +10616,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23">
@@ -9743,7 +10626,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24">
@@ -9753,7 +10636,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.82</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="25">
@@ -9763,7 +10646,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.92</v>
+        <v>6.17</v>
       </c>
     </row>
     <row r="26">
@@ -9773,7 +10656,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.79</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="27">
@@ -9793,7 +10676,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
     </row>
     <row r="29">
